--- a/template/Calculadora_Terrenos_Template.xlsx
+++ b/template/Calculadora_Terrenos_Template.xlsx
@@ -76,7 +76,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
@@ -107,77 +107,84 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2) Aba "Decks" (opcional): um deck por linha. Deixe "Auto" onde não souber: o site descobre sozinho. Preencher só ajuda a refinar.</t>
+          <t xml:space="preserve">   Dica: dá para colar direto a lista exportada do Archidekt (More &gt; Export deck &gt; Text) na coluna Carta, linha por linha, como "1x Sol Ring (c21) 263 [Ramp]". Cartas em Maybeboard são ignoradas.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2) Aba "Decks" (opcional): um deck por linha. Deixe "Auto" onde não souber: o site descobre sozinho. Preencher só ajuda a refinar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">3) Salve o arquivo e envie no site. Você recebe o número de terrenos recomendado por deck e pode baixar o resultado em Excel.</t>
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">O que cada campo significa</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Arquétipo: Aggro, Tempo, Midrange, Control, Combo, Ramp ou Lands. Auto = o site sugere pelo nome do deck e pelas cartas (mesmas regras do TCC).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tamanho: 40, 60 ou 100 cartas. Auto = pelo total do main deck.</t>
+          <t xml:space="preserve">Arquétipo: Aggro, Tempo, Midrange, Control, Combo, Ramp ou Lands. Auto = o site sugere pelo nome do deck e pelas cartas (mesmas regras do TCC).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Companion: Sim/Não. Auto = detecta se há uma carta com Companion no sideboard.</t>
+          <t xml:space="preserve">Tamanho: 40, 60 ou 100 cartas. Auto = pelo total do main deck.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Companion: Sim/Não. Auto = detecta se há uma carta com Companion no sideboard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Cores: letras WUBRG (W branco, U azul, B preto, R vermelho, G verde), ex.: UB. Vazio = detecta pelo nome do deck, terrenos básicos ou cores das mágicas.</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Como o número é calculado</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Regressão linear múltipla (Penatti &amp; Costa, 2026) sobre 39.287 decks vencedores, com custo médio de mana, compra e aceleração baratas (CMC ≤ 2), companion, número de cores, arquétipo e interação cor × arquétipo. Estende o modelo de Frank Karsten (TCGplayer, 2022). As cartas são lidas ao vivo no Scryfall, então sets novos entram automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDFC terreno/mágica contam como 0,38 terreno (não míticos) ou 0,74 (míticos). Para 40 e 100 cartas, a fórmula é escalada proporcionalmente (aproximação).</t>
+          <t xml:space="preserve">Regressão linear múltipla (Penatti &amp; Costa, 2026) sobre 39.287 decks vencedores, com custo médio de mana, compra e aceleração baratas (CMC ≤ 2), companion, número de cores, arquétipo e interação cor × arquétipo. Estende o modelo de Frank Karsten (TCGplayer, 2022). As cartas são lidas ao vivo no Scryfall, então sets novos entram automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MDFC terreno/mágica contam como 0,38 terreno (não míticos) ou 0,74 (míticos). Para 40 e 100 cartas, a fórmula é escalada proporcionalmente (aproximação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">O resultado é um ponto de partida: o erro típico do modelo é de cerca de ±1,8 terreno.</t>
         </is>
